--- a/02_加值成品/歷屆試題/115年會考自然科.xlsx
+++ b/02_加值成品/歷屆試題/115年會考自然科.xlsx
@@ -1079,10 +1079,26 @@
           <t>小芳連續14天朝南方觀察住家附近的月相，其中第8天到第14天的月相如圖(九)。根據觀察結果，下列何者最可能是他前7天所觀察到的月相變化？</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>C</t>
@@ -1743,10 +1759,26 @@
           <t>下列選項為在金屬鑰匙上鍍銅的電鍍裝置示意圖，圖中直流電源正、負極的標示和電鍍液中銅離子的移動方向，何者正確？</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
           <t>B</t>
@@ -2007,10 +2039,26 @@
           <t>圖(二十三)為嘉義在6/1～隔年1/1的白天時數變化圖，已知某城市位於北半球且緯度比臺灣高，則下列有關此城市與嘉義在相同日期間的白天時數圖，何者最合理？</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr"/>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="7" t="inlineStr"/>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
           <t>C</t>
@@ -2351,10 +2399,26 @@
           <t>根據本文，已知石英板作用在水滴的力為F′，F′即F的反作用力，則圖(三十一)中呈現的四個狀態，哪一個狀態下F′的大小最大？</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>(圖形選項，請見官方題本PDF)</t>
+        </is>
+      </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
           <t>A</t>
